--- a/Mastercard Consulting/GreenTrail Store Data.xlsx
+++ b/Mastercard Consulting/GreenTrail Store Data.xlsx
@@ -1,21 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11028"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30425"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gcforage/Desktop/Forage Working Docs/Mastercard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2050C21-3C4A-D34F-B426-40232578412C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="24" documentId="13_ncr:1_{A2050C21-3C4A-D34F-B426-40232578412C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BC637EF3-F630-4BBE-B515-387361269EEA}"/>
   <bookViews>
-    <workbookView xWindow="380" yWindow="500" windowWidth="28040" windowHeight="16340" xr2:uid="{9254BF81-C7BC-8144-BBAF-D515DF4C6537}"/>
+    <workbookView xWindow="380" yWindow="500" windowWidth="28040" windowHeight="16340" activeTab="1" xr2:uid="{9254BF81-C7BC-8144-BBAF-D515DF4C6537}"/>
   </bookViews>
   <sheets>
     <sheet name="Store Data" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191028"/>
+  <pivotCaches>
+    <pivotCache cacheId="111" r:id="rId3"/>
+  </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="50">
   <si>
     <t>Store ID</t>
   </si>
@@ -71,6 +75,27 @@
     <t>Weekly Sales After Promotion</t>
   </si>
   <si>
+    <t>Average Daily Visits During Promotion</t>
+  </si>
+  <si>
+    <t>Average Daily Visits Before Promotion</t>
+  </si>
+  <si>
+    <t>Average Daily Visits After Promotion</t>
+  </si>
+  <si>
+    <t>Sales uplift</t>
+  </si>
+  <si>
+    <t>Post-promotion retention</t>
+  </si>
+  <si>
+    <t>Visit uplift</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Promotion Duration </t>
+  </si>
+  <si>
     <t>New York</t>
   </si>
   <si>
@@ -161,13 +186,10 @@
     <t>Milwaukee</t>
   </si>
   <si>
-    <t>Average Daily Visits During Promotion</t>
-  </si>
-  <si>
-    <t>Average Daily Visits Before Promotion</t>
-  </si>
-  <si>
-    <t>Average Daily Visits After Promotion</t>
+    <t>Average of Weekly Sales During Promotion</t>
+  </si>
+  <si>
+    <t>Grand Total</t>
   </si>
 </sst>
 </file>
@@ -175,11 +197,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
-    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="166" formatCode="000"/>
-    <numFmt numFmtId="167" formatCode="&quot;$&quot;#,##0.00"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="165" formatCode="000"/>
+    <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -193,6 +215,13 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -216,18 +245,66 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="10">
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="000"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -238,6 +315,723 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Excel Services" refreshedDate="46268.563970254632" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="25" xr:uid="{BCE18FDD-B169-4F7E-A9E9-5C206AD005CB}">
+  <cacheSource type="worksheet">
+    <worksheetSource name="Table1"/>
+  </cacheSource>
+  <cacheFields count="18">
+    <cacheField name="Store ID" numFmtId="165">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="25"/>
+    </cacheField>
+    <cacheField name="Location" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="Store Size" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1300" maxValue="2000"/>
+    </cacheField>
+    <cacheField name="Store Type" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="Promotion ID" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="101" maxValue="125"/>
+    </cacheField>
+    <cacheField name="Type of Promotion" numFmtId="0">
+      <sharedItems count="3">
+        <s v="Discount"/>
+        <s v="Buy-One-Get-One"/>
+        <s v="Special Event"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Promotion Start Date" numFmtId="164">
+      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2023-04-10T00:00:00" maxDate="2023-08-16T00:00:00"/>
+    </cacheField>
+    <cacheField name="Promotion End Date" numFmtId="164">
+      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2023-04-24T00:00:00" maxDate="2023-08-30T00:00:00"/>
+    </cacheField>
+    <cacheField name="Weekly Sales During Promotion" numFmtId="166">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="42000" maxValue="60000" count="17">
+        <n v="50000"/>
+        <n v="45000"/>
+        <n v="60000"/>
+        <n v="48000"/>
+        <n v="53000"/>
+        <n v="49000"/>
+        <n v="42000"/>
+        <n v="56000"/>
+        <n v="47000"/>
+        <n v="52000"/>
+        <n v="51000"/>
+        <n v="43000"/>
+        <n v="55000"/>
+        <n v="46000"/>
+        <n v="58000"/>
+        <n v="44000"/>
+        <n v="54000"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Weekly Sales Before Promotion" numFmtId="166">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="30000" maxValue="44000"/>
+    </cacheField>
+    <cacheField name="Weekly Sales After Promotion" numFmtId="166">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="30000" maxValue="45000"/>
+    </cacheField>
+    <cacheField name="Average Daily Visits During Promotion" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="350" maxValue="540"/>
+    </cacheField>
+    <cacheField name="Average Daily Visits Before Promotion" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="300" maxValue="430"/>
+    </cacheField>
+    <cacheField name="Average Daily Visits After Promotion" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="320" maxValue="450"/>
+    </cacheField>
+    <cacheField name="Sales uplift" numFmtId="166">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="2000" maxValue="20000"/>
+    </cacheField>
+    <cacheField name="Post-promotion retention" numFmtId="166">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="-5000" maxValue="10000"/>
+    </cacheField>
+    <cacheField name="Visit uplift" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="-10" maxValue="120"/>
+    </cacheField>
+    <cacheField name="Promotion Duration " numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="13" maxValue="14"/>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="25">
+  <r>
+    <n v="1"/>
+    <s v="New York"/>
+    <n v="2000"/>
+    <s v="Urban"/>
+    <n v="101"/>
+    <x v="0"/>
+    <d v="2023-06-01T00:00:00"/>
+    <d v="2023-06-14T00:00:00"/>
+    <x v="0"/>
+    <n v="30000"/>
+    <n v="35000"/>
+    <n v="400"/>
+    <n v="300"/>
+    <n v="350"/>
+    <n v="20000"/>
+    <n v="5000"/>
+    <n v="50"/>
+    <n v="13"/>
+  </r>
+  <r>
+    <n v="2"/>
+    <s v="Los Angeles"/>
+    <n v="1500"/>
+    <s v="Suburban"/>
+    <n v="102"/>
+    <x v="1"/>
+    <d v="2023-05-15T00:00:00"/>
+    <d v="2023-05-28T00:00:00"/>
+    <x v="1"/>
+    <n v="35000"/>
+    <n v="30000"/>
+    <n v="450"/>
+    <n v="400"/>
+    <n v="375"/>
+    <n v="10000"/>
+    <n v="-5000"/>
+    <n v="75"/>
+    <n v="13"/>
+  </r>
+  <r>
+    <n v="3"/>
+    <s v="Chicago"/>
+    <n v="1800"/>
+    <s v="Urban"/>
+    <n v="103"/>
+    <x v="2"/>
+    <d v="2023-07-01T00:00:00"/>
+    <d v="2023-07-14T00:00:00"/>
+    <x v="2"/>
+    <n v="40000"/>
+    <n v="40000"/>
+    <n v="500"/>
+    <n v="350"/>
+    <n v="450"/>
+    <n v="20000"/>
+    <n v="0"/>
+    <n v="50"/>
+    <n v="13"/>
+  </r>
+  <r>
+    <n v="4"/>
+    <s v="Houston"/>
+    <n v="1600"/>
+    <s v="Suburban"/>
+    <n v="104"/>
+    <x v="0"/>
+    <d v="2023-06-10T00:00:00"/>
+    <d v="2023-06-24T00:00:00"/>
+    <x v="3"/>
+    <n v="32000"/>
+    <n v="33000"/>
+    <n v="425"/>
+    <n v="310"/>
+    <n v="320"/>
+    <n v="16000"/>
+    <n v="1000"/>
+    <n v="105"/>
+    <n v="14"/>
+  </r>
+  <r>
+    <n v="5"/>
+    <s v="Phoenix"/>
+    <n v="1700"/>
+    <s v="Urban"/>
+    <n v="105"/>
+    <x v="1"/>
+    <d v="2023-04-20T00:00:00"/>
+    <d v="2023-05-04T00:00:00"/>
+    <x v="4"/>
+    <n v="34000"/>
+    <n v="36000"/>
+    <n v="475"/>
+    <n v="350"/>
+    <n v="370"/>
+    <n v="19000"/>
+    <n v="2000"/>
+    <n v="105"/>
+    <n v="14"/>
+  </r>
+  <r>
+    <n v="6"/>
+    <s v="Philadelphia"/>
+    <n v="1800"/>
+    <s v="Urban"/>
+    <n v="106"/>
+    <x v="2"/>
+    <d v="2023-08-05T00:00:00"/>
+    <d v="2023-08-19T00:00:00"/>
+    <x v="5"/>
+    <n v="31000"/>
+    <n v="41000"/>
+    <n v="480"/>
+    <n v="300"/>
+    <n v="400"/>
+    <n v="18000"/>
+    <n v="10000"/>
+    <n v="80"/>
+    <n v="14"/>
+  </r>
+  <r>
+    <n v="7"/>
+    <s v="San Antonio"/>
+    <n v="1400"/>
+    <s v="Suburban"/>
+    <n v="107"/>
+    <x v="0"/>
+    <d v="2023-07-15T00:00:00"/>
+    <d v="2023-07-29T00:00:00"/>
+    <x v="6"/>
+    <n v="39000"/>
+    <n v="37000"/>
+    <n v="350"/>
+    <n v="340"/>
+    <n v="360"/>
+    <n v="3000"/>
+    <n v="-2000"/>
+    <n v="-10"/>
+    <n v="14"/>
+  </r>
+  <r>
+    <n v="8"/>
+    <s v="San Diego"/>
+    <n v="2000"/>
+    <s v="Urban"/>
+    <n v="108"/>
+    <x v="1"/>
+    <d v="2023-06-22T00:00:00"/>
+    <d v="2023-07-06T00:00:00"/>
+    <x v="7"/>
+    <n v="43000"/>
+    <n v="39000"/>
+    <n v="530"/>
+    <n v="420"/>
+    <n v="410"/>
+    <n v="13000"/>
+    <n v="-4000"/>
+    <n v="120"/>
+    <n v="14"/>
+  </r>
+  <r>
+    <n v="9"/>
+    <s v="Dallas"/>
+    <n v="1500"/>
+    <s v="Suburban"/>
+    <n v="109"/>
+    <x v="2"/>
+    <d v="2023-05-10T00:00:00"/>
+    <d v="2023-05-24T00:00:00"/>
+    <x v="8"/>
+    <n v="36000"/>
+    <n v="38000"/>
+    <n v="420"/>
+    <n v="365"/>
+    <n v="380"/>
+    <n v="11000"/>
+    <n v="2000"/>
+    <n v="40"/>
+    <n v="14"/>
+  </r>
+  <r>
+    <n v="10"/>
+    <s v="San Jose"/>
+    <n v="1750"/>
+    <s v="Urban"/>
+    <n v="110"/>
+    <x v="0"/>
+    <d v="2023-04-15T00:00:00"/>
+    <d v="2023-04-29T00:00:00"/>
+    <x v="9"/>
+    <n v="33000"/>
+    <n v="41000"/>
+    <n v="500"/>
+    <n v="320"/>
+    <n v="390"/>
+    <n v="19000"/>
+    <n v="8000"/>
+    <n v="110"/>
+    <n v="14"/>
+  </r>
+  <r>
+    <n v="11"/>
+    <s v="Austin"/>
+    <n v="1600"/>
+    <s v="Suburban"/>
+    <n v="111"/>
+    <x v="1"/>
+    <d v="2023-08-01T00:00:00"/>
+    <d v="2023-08-15T00:00:00"/>
+    <x v="1"/>
+    <n v="37000"/>
+    <n v="34000"/>
+    <n v="410"/>
+    <n v="370"/>
+    <n v="350"/>
+    <n v="8000"/>
+    <n v="-3000"/>
+    <n v="60"/>
+    <n v="14"/>
+  </r>
+  <r>
+    <n v="12"/>
+    <s v="Jacksonville"/>
+    <n v="1450"/>
+    <s v="Urban"/>
+    <n v="112"/>
+    <x v="2"/>
+    <d v="2023-07-20T00:00:00"/>
+    <d v="2023-08-03T00:00:00"/>
+    <x v="10"/>
+    <n v="38000"/>
+    <n v="42000"/>
+    <n v="470"/>
+    <n v="360"/>
+    <n v="410"/>
+    <n v="13000"/>
+    <n v="4000"/>
+    <n v="60"/>
+    <n v="14"/>
+  </r>
+  <r>
+    <n v="13"/>
+    <s v="Fort Worth"/>
+    <n v="1550"/>
+    <s v="Suburban"/>
+    <n v="113"/>
+    <x v="0"/>
+    <d v="2023-06-18T00:00:00"/>
+    <d v="2023-07-02T00:00:00"/>
+    <x v="11"/>
+    <n v="35000"/>
+    <n v="36000"/>
+    <n v="400"/>
+    <n v="340"/>
+    <n v="350"/>
+    <n v="8000"/>
+    <n v="1000"/>
+    <n v="50"/>
+    <n v="14"/>
+  </r>
+  <r>
+    <n v="14"/>
+    <s v="Columbus"/>
+    <n v="1650"/>
+    <s v="Urban"/>
+    <n v="114"/>
+    <x v="1"/>
+    <d v="2023-05-25T00:00:00"/>
+    <d v="2023-06-08T00:00:00"/>
+    <x v="12"/>
+    <n v="41000"/>
+    <n v="45000"/>
+    <n v="520"/>
+    <n v="400"/>
+    <n v="430"/>
+    <n v="14000"/>
+    <n v="4000"/>
+    <n v="90"/>
+    <n v="14"/>
+  </r>
+  <r>
+    <n v="15"/>
+    <s v="Charlotte"/>
+    <n v="1750"/>
+    <s v="Suburban"/>
+    <n v="115"/>
+    <x v="2"/>
+    <d v="2023-04-30T00:00:00"/>
+    <d v="2023-05-14T00:00:00"/>
+    <x v="13"/>
+    <n v="34000"/>
+    <n v="37000"/>
+    <n v="415"/>
+    <n v="335"/>
+    <n v="360"/>
+    <n v="12000"/>
+    <n v="3000"/>
+    <n v="55"/>
+    <n v="14"/>
+  </r>
+  <r>
+    <n v="16"/>
+    <s v="Detroit"/>
+    <n v="1900"/>
+    <s v="Urban"/>
+    <n v="116"/>
+    <x v="0"/>
+    <d v="2023-08-10T00:00:00"/>
+    <d v="2023-08-24T00:00:00"/>
+    <x v="14"/>
+    <n v="44000"/>
+    <n v="42000"/>
+    <n v="540"/>
+    <n v="430"/>
+    <n v="420"/>
+    <n v="14000"/>
+    <n v="-2000"/>
+    <n v="120"/>
+    <n v="14"/>
+  </r>
+  <r>
+    <n v="17"/>
+    <s v="El Paso"/>
+    <n v="1300"/>
+    <s v="Suburban"/>
+    <n v="117"/>
+    <x v="1"/>
+    <d v="2023-07-12T00:00:00"/>
+    <d v="2023-07-26T00:00:00"/>
+    <x v="15"/>
+    <n v="42000"/>
+    <n v="40000"/>
+    <n v="390"/>
+    <n v="380"/>
+    <n v="370"/>
+    <n v="2000"/>
+    <n v="-2000"/>
+    <n v="20"/>
+    <n v="14"/>
+  </r>
+  <r>
+    <n v="18"/>
+    <s v="Memphis"/>
+    <n v="1450"/>
+    <s v="Urban"/>
+    <n v="118"/>
+    <x v="2"/>
+    <d v="2023-06-15T00:00:00"/>
+    <d v="2023-06-29T00:00:00"/>
+    <x v="8"/>
+    <n v="35000"/>
+    <n v="39000"/>
+    <n v="410"/>
+    <n v="330"/>
+    <n v="380"/>
+    <n v="12000"/>
+    <n v="4000"/>
+    <n v="30"/>
+    <n v="14"/>
+  </r>
+  <r>
+    <n v="19"/>
+    <s v="Baltimore"/>
+    <n v="1500"/>
+    <s v="Suburban"/>
+    <n v="119"/>
+    <x v="0"/>
+    <d v="2023-05-05T00:00:00"/>
+    <d v="2023-05-19T00:00:00"/>
+    <x v="5"/>
+    <n v="37000"/>
+    <n v="36000"/>
+    <n v="420"/>
+    <n v="360"/>
+    <n v="350"/>
+    <n v="12000"/>
+    <n v="-1000"/>
+    <n v="70"/>
+    <n v="14"/>
+  </r>
+  <r>
+    <n v="20"/>
+    <s v="Boston"/>
+    <n v="1650"/>
+    <s v="Urban"/>
+    <n v="120"/>
+    <x v="1"/>
+    <d v="2023-04-10T00:00:00"/>
+    <d v="2023-04-24T00:00:00"/>
+    <x v="16"/>
+    <n v="40000"/>
+    <n v="41000"/>
+    <n v="510"/>
+    <n v="390"/>
+    <n v="400"/>
+    <n v="14000"/>
+    <n v="1000"/>
+    <n v="110"/>
+    <n v="14"/>
+  </r>
+  <r>
+    <n v="21"/>
+    <s v="Nashville"/>
+    <n v="1550"/>
+    <s v="Suburban"/>
+    <n v="121"/>
+    <x v="2"/>
+    <d v="2023-08-15T00:00:00"/>
+    <d v="2023-08-29T00:00:00"/>
+    <x v="1"/>
+    <n v="33000"/>
+    <n v="35000"/>
+    <n v="400"/>
+    <n v="320"/>
+    <n v="330"/>
+    <n v="12000"/>
+    <n v="2000"/>
+    <n v="70"/>
+    <n v="14"/>
+  </r>
+  <r>
+    <n v="22"/>
+    <s v="Denver"/>
+    <n v="1600"/>
+    <s v="Urban"/>
+    <n v="122"/>
+    <x v="0"/>
+    <d v="2023-07-18T00:00:00"/>
+    <d v="2023-08-01T00:00:00"/>
+    <x v="0"/>
+    <n v="39000"/>
+    <n v="42000"/>
+    <n v="480"/>
+    <n v="370"/>
+    <n v="400"/>
+    <n v="11000"/>
+    <n v="3000"/>
+    <n v="80"/>
+    <n v="14"/>
+  </r>
+  <r>
+    <n v="23"/>
+    <s v="Louisville"/>
+    <n v="1350"/>
+    <s v="Suburban"/>
+    <n v="123"/>
+    <x v="1"/>
+    <d v="2023-06-20T00:00:00"/>
+    <d v="2023-07-04T00:00:00"/>
+    <x v="3"/>
+    <n v="36000"/>
+    <n v="37000"/>
+    <n v="410"/>
+    <n v="350"/>
+    <n v="360"/>
+    <n v="12000"/>
+    <n v="1000"/>
+    <n v="50"/>
+    <n v="14"/>
+  </r>
+  <r>
+    <n v="24"/>
+    <s v="Portland"/>
+    <n v="1400"/>
+    <s v="Urban"/>
+    <n v="124"/>
+    <x v="2"/>
+    <d v="2023-05-15T00:00:00"/>
+    <d v="2023-05-29T00:00:00"/>
+    <x v="9"/>
+    <n v="41000"/>
+    <n v="43000"/>
+    <n v="470"/>
+    <n v="400"/>
+    <n v="420"/>
+    <n v="11000"/>
+    <n v="2000"/>
+    <n v="50"/>
+    <n v="14"/>
+  </r>
+  <r>
+    <n v="25"/>
+    <s v="Milwaukee"/>
+    <n v="1500"/>
+    <s v="Suburban"/>
+    <n v="125"/>
+    <x v="0"/>
+    <d v="2023-04-20T00:00:00"/>
+    <d v="2023-05-04T00:00:00"/>
+    <x v="8"/>
+    <n v="35000"/>
+    <n v="38000"/>
+    <n v="400"/>
+    <n v="340"/>
+    <n v="370"/>
+    <n v="12000"/>
+    <n v="3000"/>
+    <n v="30"/>
+    <n v="14"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{AEF79952-1A59-4A64-92CF-90D866CAC856}" name="PivotTable1" cacheId="111" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+  <location ref="A1:B5" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="18">
+    <pivotField compact="0" numFmtId="165" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField axis="axisRow" compact="0" outline="0" showAll="0">
+      <items count="4">
+        <item x="1"/>
+        <item x="0"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" numFmtId="164" outline="0" showAll="0"/>
+    <pivotField compact="0" numFmtId="164" outline="0" showAll="0"/>
+    <pivotField dataField="1" compact="0" numFmtId="166" outline="0" showAll="0">
+      <items count="18">
+        <item x="6"/>
+        <item x="11"/>
+        <item x="15"/>
+        <item x="1"/>
+        <item x="13"/>
+        <item x="8"/>
+        <item x="3"/>
+        <item x="5"/>
+        <item x="0"/>
+        <item x="10"/>
+        <item x="9"/>
+        <item x="4"/>
+        <item x="16"/>
+        <item x="12"/>
+        <item x="7"/>
+        <item x="14"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" numFmtId="166" outline="0" showAll="0"/>
+    <pivotField compact="0" numFmtId="166" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" numFmtId="166" outline="0" showAll="0"/>
+    <pivotField compact="0" numFmtId="166" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="5"/>
+  </rowFields>
+  <rowItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Average of Weekly Sales During Promotion" fld="8" subtotal="average" baseField="0" baseItem="0" numFmtId="166"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{67DB6C05-6878-4968-B378-95644011D360}" name="Table1" displayName="Table1" ref="A1:R26" totalsRowShown="0" headerRowDxfId="9">
+  <autoFilter ref="A1:R26" xr:uid="{67DB6C05-6878-4968-B378-95644011D360}"/>
+  <tableColumns count="18">
+    <tableColumn id="1" xr3:uid="{3DDDBCF6-C850-4502-8271-F5B7BAA19E23}" name="Store ID" dataDxfId="8"/>
+    <tableColumn id="2" xr3:uid="{3070932D-D8F5-4248-A8B8-90C224371E06}" name="Location"/>
+    <tableColumn id="3" xr3:uid="{E4D3A266-C41B-463F-A488-B72743E07345}" name="Store Size"/>
+    <tableColumn id="4" xr3:uid="{4D9714C5-C48E-4A84-9F8B-554C8A1F4276}" name="Store Type"/>
+    <tableColumn id="5" xr3:uid="{91D230CC-6334-43BA-89E0-5D53FF2B2EED}" name="Promotion ID"/>
+    <tableColumn id="6" xr3:uid="{F636231E-A6B4-467D-8451-F6DD8EF9E149}" name="Type of Promotion"/>
+    <tableColumn id="7" xr3:uid="{322DCF1F-B304-4019-9AF9-20C677AF0BB8}" name="Promotion Start Date" dataDxfId="7"/>
+    <tableColumn id="8" xr3:uid="{D429060B-7E3E-43A5-9A5A-C178F8141D80}" name="Promotion End Date" dataDxfId="6"/>
+    <tableColumn id="9" xr3:uid="{79A5A1C0-4DA2-4231-A2A7-211348B4A320}" name="Weekly Sales During Promotion" dataDxfId="5"/>
+    <tableColumn id="10" xr3:uid="{FAE3A862-3C4F-4AA8-83BB-DCE6F01D78A0}" name="Weekly Sales Before Promotion" dataDxfId="4"/>
+    <tableColumn id="11" xr3:uid="{AAB915E7-2D7A-4B15-A8A5-23EE9387A797}" name="Weekly Sales After Promotion" dataDxfId="3"/>
+    <tableColumn id="12" xr3:uid="{3E54798D-EECD-4A7F-8A51-E7F43261E1D4}" name="Average Daily Visits During Promotion"/>
+    <tableColumn id="13" xr3:uid="{D980C5F4-66E6-43CC-A570-129F73BB38A3}" name="Average Daily Visits Before Promotion"/>
+    <tableColumn id="14" xr3:uid="{07BF2D0A-362D-45DC-A96E-86CDE0EAFF13}" name="Average Daily Visits After Promotion"/>
+    <tableColumn id="15" xr3:uid="{D85320B9-22AF-443C-8424-4DA1E8E199DF}" name="Sales uplift" dataDxfId="2">
+      <calculatedColumnFormula>I2-J2</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="16" xr3:uid="{D0047790-DCE0-4C33-AE3A-309A921F1628}" name="Post-promotion retention" dataDxfId="1">
+      <calculatedColumnFormula>K2-J2</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="17" xr3:uid="{43F43850-5289-405E-83B7-23BF1B17E920}" name="Visit uplift">
+      <calculatedColumnFormula>L2-N2</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="18" xr3:uid="{EACF523A-7BF2-4A2F-AFF2-4FCF105C1FA3}" name="Promotion Duration " dataDxfId="0">
+      <calculatedColumnFormula>Table1[[#This Row],[Promotion End Date]]-Table1[[#This Row],[Promotion Start Date]]</calculatedColumnFormula>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -537,24 +1331,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFFF4F8D-85C0-AD4A-84D6-E41ACF3D7A83}">
-  <dimension ref="A1:N26"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:R26"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.95"/>
   <cols>
-    <col min="1" max="1" width="7.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.1640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.83203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="27.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.625" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="11.125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="21" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="27.375" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="27.5" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="26" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="32.83203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="26.875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="32.875" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="33" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="31.5" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="24.75" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="11.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:18" ht="15.75">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -589,33 +1387,45 @@
         <v>10</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>41</v>
+        <v>11</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>42</v>
+        <v>12</v>
       </c>
       <c r="N1" s="3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+      <c r="O1" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18">
       <c r="A2" s="2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="C2">
         <v>2000</v>
       </c>
       <c r="D2" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E2">
         <v>101</v>
       </c>
       <c r="F2" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="G2" s="1">
         <v>45078</v>
@@ -641,25 +1451,41 @@
       <c r="N2">
         <v>350</v>
       </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O2" s="5">
+        <f>I2-J2</f>
+        <v>20000</v>
+      </c>
+      <c r="P2" s="5">
+        <f>K2-J2</f>
+        <v>5000</v>
+      </c>
+      <c r="Q2">
+        <f>L2-N2</f>
+        <v>50</v>
+      </c>
+      <c r="R2">
+        <f>Table1[[#This Row],[Promotion End Date]]-Table1[[#This Row],[Promotion Start Date]]</f>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18">
       <c r="A3" s="2">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="C3">
         <v>1500</v>
       </c>
       <c r="D3" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E3">
         <v>102</v>
       </c>
       <c r="F3" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="G3" s="1">
         <v>45061</v>
@@ -685,25 +1511,41 @@
       <c r="N3">
         <v>375</v>
       </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O3" s="5">
+        <f t="shared" ref="O3:O26" si="0">I3-J3</f>
+        <v>10000</v>
+      </c>
+      <c r="P3" s="5">
+        <f t="shared" ref="P3:P26" si="1">K3-J3</f>
+        <v>-5000</v>
+      </c>
+      <c r="Q3">
+        <f t="shared" ref="Q3:Q26" si="2">L3-N3</f>
+        <v>75</v>
+      </c>
+      <c r="R3">
+        <f>Table1[[#This Row],[Promotion End Date]]-Table1[[#This Row],[Promotion Start Date]]</f>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18">
       <c r="A4" s="2">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="C4">
         <v>1800</v>
       </c>
       <c r="D4" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E4">
         <v>103</v>
       </c>
       <c r="F4" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="G4" s="1">
         <v>45108</v>
@@ -729,25 +1571,41 @@
       <c r="N4">
         <v>450</v>
       </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O4" s="5">
+        <f t="shared" si="0"/>
+        <v>20000</v>
+      </c>
+      <c r="P4" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q4">
+        <f t="shared" si="2"/>
+        <v>50</v>
+      </c>
+      <c r="R4">
+        <f>Table1[[#This Row],[Promotion End Date]]-Table1[[#This Row],[Promotion Start Date]]</f>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18">
       <c r="A5" s="2">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="C5">
         <v>1600</v>
       </c>
       <c r="D5" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E5">
         <v>104</v>
       </c>
       <c r="F5" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="G5" s="1">
         <v>45087</v>
@@ -773,25 +1631,41 @@
       <c r="N5">
         <v>320</v>
       </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O5" s="5">
+        <f t="shared" si="0"/>
+        <v>16000</v>
+      </c>
+      <c r="P5" s="5">
+        <f t="shared" si="1"/>
+        <v>1000</v>
+      </c>
+      <c r="Q5">
+        <f t="shared" si="2"/>
+        <v>105</v>
+      </c>
+      <c r="R5">
+        <f>Table1[[#This Row],[Promotion End Date]]-Table1[[#This Row],[Promotion Start Date]]</f>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18">
       <c r="A6" s="2">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="C6">
         <v>1700</v>
       </c>
       <c r="D6" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E6">
         <v>105</v>
       </c>
       <c r="F6" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="G6" s="1">
         <v>45036</v>
@@ -817,25 +1691,41 @@
       <c r="N6">
         <v>370</v>
       </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O6" s="5">
+        <f t="shared" si="0"/>
+        <v>19000</v>
+      </c>
+      <c r="P6" s="5">
+        <f t="shared" si="1"/>
+        <v>2000</v>
+      </c>
+      <c r="Q6">
+        <f t="shared" si="2"/>
+        <v>105</v>
+      </c>
+      <c r="R6">
+        <f>Table1[[#This Row],[Promotion End Date]]-Table1[[#This Row],[Promotion Start Date]]</f>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18">
       <c r="A7" s="2">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="C7">
         <v>1800</v>
       </c>
       <c r="D7" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E7">
         <v>106</v>
       </c>
       <c r="F7" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="G7" s="1">
         <v>45143</v>
@@ -861,25 +1751,41 @@
       <c r="N7">
         <v>400</v>
       </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O7" s="5">
+        <f t="shared" si="0"/>
+        <v>18000</v>
+      </c>
+      <c r="P7" s="5">
+        <f t="shared" si="1"/>
+        <v>10000</v>
+      </c>
+      <c r="Q7">
+        <f t="shared" si="2"/>
+        <v>80</v>
+      </c>
+      <c r="R7">
+        <f>Table1[[#This Row],[Promotion End Date]]-Table1[[#This Row],[Promotion Start Date]]</f>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18">
       <c r="A8" s="2">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="C8">
         <v>1400</v>
       </c>
       <c r="D8" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E8">
         <v>107</v>
       </c>
       <c r="F8" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="G8" s="1">
         <v>45122</v>
@@ -905,25 +1811,41 @@
       <c r="N8">
         <v>360</v>
       </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O8" s="5">
+        <f t="shared" si="0"/>
+        <v>3000</v>
+      </c>
+      <c r="P8" s="5">
+        <f t="shared" si="1"/>
+        <v>-2000</v>
+      </c>
+      <c r="Q8">
+        <f t="shared" si="2"/>
+        <v>-10</v>
+      </c>
+      <c r="R8">
+        <f>Table1[[#This Row],[Promotion End Date]]-Table1[[#This Row],[Promotion Start Date]]</f>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18">
       <c r="A9" s="2">
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="C9">
         <v>2000</v>
       </c>
       <c r="D9" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E9">
         <v>108</v>
       </c>
       <c r="F9" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="G9" s="1">
         <v>45099</v>
@@ -949,25 +1871,41 @@
       <c r="N9">
         <v>410</v>
       </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O9" s="5">
+        <f t="shared" si="0"/>
+        <v>13000</v>
+      </c>
+      <c r="P9" s="5">
+        <f t="shared" si="1"/>
+        <v>-4000</v>
+      </c>
+      <c r="Q9">
+        <f t="shared" si="2"/>
+        <v>120</v>
+      </c>
+      <c r="R9">
+        <f>Table1[[#This Row],[Promotion End Date]]-Table1[[#This Row],[Promotion Start Date]]</f>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18">
       <c r="A10" s="2">
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C10">
         <v>1500</v>
       </c>
       <c r="D10" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E10">
         <v>109</v>
       </c>
       <c r="F10" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="G10" s="1">
         <v>45056</v>
@@ -993,25 +1931,41 @@
       <c r="N10">
         <v>380</v>
       </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O10" s="5">
+        <f t="shared" si="0"/>
+        <v>11000</v>
+      </c>
+      <c r="P10" s="5">
+        <f t="shared" si="1"/>
+        <v>2000</v>
+      </c>
+      <c r="Q10">
+        <f t="shared" si="2"/>
+        <v>40</v>
+      </c>
+      <c r="R10">
+        <f>Table1[[#This Row],[Promotion End Date]]-Table1[[#This Row],[Promotion Start Date]]</f>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18">
       <c r="A11" s="2">
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="C11">
         <v>1750</v>
       </c>
       <c r="D11" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E11">
         <v>110</v>
       </c>
       <c r="F11" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="G11" s="1">
         <v>45031</v>
@@ -1037,25 +1991,41 @@
       <c r="N11">
         <v>390</v>
       </c>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O11" s="5">
+        <f t="shared" si="0"/>
+        <v>19000</v>
+      </c>
+      <c r="P11" s="5">
+        <f t="shared" si="1"/>
+        <v>8000</v>
+      </c>
+      <c r="Q11">
+        <f t="shared" si="2"/>
+        <v>110</v>
+      </c>
+      <c r="R11">
+        <f>Table1[[#This Row],[Promotion End Date]]-Table1[[#This Row],[Promotion Start Date]]</f>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18">
       <c r="A12" s="2">
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="C12">
         <v>1600</v>
       </c>
       <c r="D12" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E12">
         <v>111</v>
       </c>
       <c r="F12" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="G12" s="1">
         <v>45139</v>
@@ -1081,25 +2051,41 @@
       <c r="N12">
         <v>350</v>
       </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O12" s="5">
+        <f t="shared" si="0"/>
+        <v>8000</v>
+      </c>
+      <c r="P12" s="5">
+        <f t="shared" si="1"/>
+        <v>-3000</v>
+      </c>
+      <c r="Q12">
+        <f t="shared" si="2"/>
+        <v>60</v>
+      </c>
+      <c r="R12">
+        <f>Table1[[#This Row],[Promotion End Date]]-Table1[[#This Row],[Promotion Start Date]]</f>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18">
       <c r="A13" s="2">
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="C13">
         <v>1450</v>
       </c>
       <c r="D13" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E13">
         <v>112</v>
       </c>
       <c r="F13" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="G13" s="1">
         <v>45127</v>
@@ -1125,25 +2111,41 @@
       <c r="N13">
         <v>410</v>
       </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O13" s="5">
+        <f t="shared" si="0"/>
+        <v>13000</v>
+      </c>
+      <c r="P13" s="5">
+        <f t="shared" si="1"/>
+        <v>4000</v>
+      </c>
+      <c r="Q13">
+        <f t="shared" si="2"/>
+        <v>60</v>
+      </c>
+      <c r="R13">
+        <f>Table1[[#This Row],[Promotion End Date]]-Table1[[#This Row],[Promotion Start Date]]</f>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18">
       <c r="A14" s="2">
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="C14">
         <v>1550</v>
       </c>
       <c r="D14" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E14">
         <v>113</v>
       </c>
       <c r="F14" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="G14" s="1">
         <v>45095</v>
@@ -1169,25 +2171,41 @@
       <c r="N14">
         <v>350</v>
       </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O14" s="5">
+        <f t="shared" si="0"/>
+        <v>8000</v>
+      </c>
+      <c r="P14" s="5">
+        <f t="shared" si="1"/>
+        <v>1000</v>
+      </c>
+      <c r="Q14">
+        <f t="shared" si="2"/>
+        <v>50</v>
+      </c>
+      <c r="R14">
+        <f>Table1[[#This Row],[Promotion End Date]]-Table1[[#This Row],[Promotion Start Date]]</f>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18">
       <c r="A15" s="2">
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="C15">
         <v>1650</v>
       </c>
       <c r="D15" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E15">
         <v>114</v>
       </c>
       <c r="F15" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="G15" s="1">
         <v>45071</v>
@@ -1213,25 +2231,41 @@
       <c r="N15">
         <v>430</v>
       </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O15" s="5">
+        <f t="shared" si="0"/>
+        <v>14000</v>
+      </c>
+      <c r="P15" s="5">
+        <f t="shared" si="1"/>
+        <v>4000</v>
+      </c>
+      <c r="Q15">
+        <f t="shared" si="2"/>
+        <v>90</v>
+      </c>
+      <c r="R15">
+        <f>Table1[[#This Row],[Promotion End Date]]-Table1[[#This Row],[Promotion Start Date]]</f>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18">
       <c r="A16" s="2">
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="C16">
         <v>1750</v>
       </c>
       <c r="D16" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E16">
         <v>115</v>
       </c>
       <c r="F16" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="G16" s="1">
         <v>45046</v>
@@ -1257,25 +2291,41 @@
       <c r="N16">
         <v>360</v>
       </c>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O16" s="5">
+        <f t="shared" si="0"/>
+        <v>12000</v>
+      </c>
+      <c r="P16" s="5">
+        <f t="shared" si="1"/>
+        <v>3000</v>
+      </c>
+      <c r="Q16">
+        <f t="shared" si="2"/>
+        <v>55</v>
+      </c>
+      <c r="R16">
+        <f>Table1[[#This Row],[Promotion End Date]]-Table1[[#This Row],[Promotion Start Date]]</f>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18">
       <c r="A17" s="2">
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="C17">
         <v>1900</v>
       </c>
       <c r="D17" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E17">
         <v>116</v>
       </c>
       <c r="F17" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="G17" s="1">
         <v>45148</v>
@@ -1301,25 +2351,41 @@
       <c r="N17">
         <v>420</v>
       </c>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O17" s="5">
+        <f t="shared" si="0"/>
+        <v>14000</v>
+      </c>
+      <c r="P17" s="5">
+        <f t="shared" si="1"/>
+        <v>-2000</v>
+      </c>
+      <c r="Q17">
+        <f t="shared" si="2"/>
+        <v>120</v>
+      </c>
+      <c r="R17">
+        <f>Table1[[#This Row],[Promotion End Date]]-Table1[[#This Row],[Promotion Start Date]]</f>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18">
       <c r="A18" s="2">
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="C18">
         <v>1300</v>
       </c>
       <c r="D18" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E18">
         <v>117</v>
       </c>
       <c r="F18" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="G18" s="1">
         <v>45119</v>
@@ -1345,25 +2411,41 @@
       <c r="N18">
         <v>370</v>
       </c>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O18" s="5">
+        <f t="shared" si="0"/>
+        <v>2000</v>
+      </c>
+      <c r="P18" s="5">
+        <f t="shared" si="1"/>
+        <v>-2000</v>
+      </c>
+      <c r="Q18">
+        <f t="shared" si="2"/>
+        <v>20</v>
+      </c>
+      <c r="R18">
+        <f>Table1[[#This Row],[Promotion End Date]]-Table1[[#This Row],[Promotion Start Date]]</f>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18">
       <c r="A19" s="2">
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="C19">
         <v>1450</v>
       </c>
       <c r="D19" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E19">
         <v>118</v>
       </c>
       <c r="F19" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="G19" s="1">
         <v>45092</v>
@@ -1389,25 +2471,41 @@
       <c r="N19">
         <v>380</v>
       </c>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O19" s="5">
+        <f t="shared" si="0"/>
+        <v>12000</v>
+      </c>
+      <c r="P19" s="5">
+        <f t="shared" si="1"/>
+        <v>4000</v>
+      </c>
+      <c r="Q19">
+        <f t="shared" si="2"/>
+        <v>30</v>
+      </c>
+      <c r="R19">
+        <f>Table1[[#This Row],[Promotion End Date]]-Table1[[#This Row],[Promotion Start Date]]</f>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18">
       <c r="A20" s="2">
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="C20">
         <v>1500</v>
       </c>
       <c r="D20" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E20">
         <v>119</v>
       </c>
       <c r="F20" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="G20" s="1">
         <v>45051</v>
@@ -1433,25 +2531,41 @@
       <c r="N20">
         <v>350</v>
       </c>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O20" s="5">
+        <f t="shared" si="0"/>
+        <v>12000</v>
+      </c>
+      <c r="P20" s="5">
+        <f t="shared" si="1"/>
+        <v>-1000</v>
+      </c>
+      <c r="Q20">
+        <f t="shared" si="2"/>
+        <v>70</v>
+      </c>
+      <c r="R20">
+        <f>Table1[[#This Row],[Promotion End Date]]-Table1[[#This Row],[Promotion Start Date]]</f>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18">
       <c r="A21" s="2">
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="C21">
         <v>1650</v>
       </c>
       <c r="D21" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E21">
         <v>120</v>
       </c>
       <c r="F21" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="G21" s="1">
         <v>45026</v>
@@ -1477,25 +2591,41 @@
       <c r="N21">
         <v>400</v>
       </c>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O21" s="5">
+        <f t="shared" si="0"/>
+        <v>14000</v>
+      </c>
+      <c r="P21" s="5">
+        <f t="shared" si="1"/>
+        <v>1000</v>
+      </c>
+      <c r="Q21">
+        <f t="shared" si="2"/>
+        <v>110</v>
+      </c>
+      <c r="R21">
+        <f>Table1[[#This Row],[Promotion End Date]]-Table1[[#This Row],[Promotion Start Date]]</f>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18">
       <c r="A22" s="2">
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="C22">
         <v>1550</v>
       </c>
       <c r="D22" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E22">
         <v>121</v>
       </c>
       <c r="F22" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="G22" s="1">
         <v>45153</v>
@@ -1521,25 +2651,41 @@
       <c r="N22">
         <v>330</v>
       </c>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O22" s="5">
+        <f t="shared" si="0"/>
+        <v>12000</v>
+      </c>
+      <c r="P22" s="5">
+        <f t="shared" si="1"/>
+        <v>2000</v>
+      </c>
+      <c r="Q22">
+        <f t="shared" si="2"/>
+        <v>70</v>
+      </c>
+      <c r="R22">
+        <f>Table1[[#This Row],[Promotion End Date]]-Table1[[#This Row],[Promotion Start Date]]</f>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18">
       <c r="A23" s="2">
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="C23">
         <v>1600</v>
       </c>
       <c r="D23" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E23">
         <v>122</v>
       </c>
       <c r="F23" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="G23" s="1">
         <v>45125</v>
@@ -1565,25 +2711,41 @@
       <c r="N23">
         <v>400</v>
       </c>
-    </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O23" s="5">
+        <f t="shared" si="0"/>
+        <v>11000</v>
+      </c>
+      <c r="P23" s="5">
+        <f t="shared" si="1"/>
+        <v>3000</v>
+      </c>
+      <c r="Q23">
+        <f t="shared" si="2"/>
+        <v>80</v>
+      </c>
+      <c r="R23">
+        <f>Table1[[#This Row],[Promotion End Date]]-Table1[[#This Row],[Promotion Start Date]]</f>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18">
       <c r="A24" s="2">
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="C24">
         <v>1350</v>
       </c>
       <c r="D24" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E24">
         <v>123</v>
       </c>
       <c r="F24" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="G24" s="1">
         <v>45097</v>
@@ -1609,25 +2771,41 @@
       <c r="N24">
         <v>360</v>
       </c>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O24" s="5">
+        <f t="shared" si="0"/>
+        <v>12000</v>
+      </c>
+      <c r="P24" s="5">
+        <f t="shared" si="1"/>
+        <v>1000</v>
+      </c>
+      <c r="Q24">
+        <f t="shared" si="2"/>
+        <v>50</v>
+      </c>
+      <c r="R24">
+        <f>Table1[[#This Row],[Promotion End Date]]-Table1[[#This Row],[Promotion Start Date]]</f>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18">
       <c r="A25" s="2">
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="C25">
         <v>1400</v>
       </c>
       <c r="D25" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E25">
         <v>124</v>
       </c>
       <c r="F25" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="G25" s="1">
         <v>45061</v>
@@ -1653,25 +2831,41 @@
       <c r="N25">
         <v>420</v>
       </c>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O25" s="5">
+        <f t="shared" si="0"/>
+        <v>11000</v>
+      </c>
+      <c r="P25" s="5">
+        <f t="shared" si="1"/>
+        <v>2000</v>
+      </c>
+      <c r="Q25">
+        <f t="shared" si="2"/>
+        <v>50</v>
+      </c>
+      <c r="R25">
+        <f>Table1[[#This Row],[Promotion End Date]]-Table1[[#This Row],[Promotion Start Date]]</f>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18">
       <c r="A26" s="2">
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="C26">
         <v>1500</v>
       </c>
       <c r="D26" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E26">
         <v>125</v>
       </c>
       <c r="F26" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="G26" s="1">
         <v>45036</v>
@@ -1696,6 +2890,81 @@
       </c>
       <c r="N26">
         <v>370</v>
+      </c>
+      <c r="O26" s="5">
+        <f t="shared" si="0"/>
+        <v>12000</v>
+      </c>
+      <c r="P26" s="5">
+        <f t="shared" si="1"/>
+        <v>3000</v>
+      </c>
+      <c r="Q26">
+        <f t="shared" si="2"/>
+        <v>30</v>
+      </c>
+      <c r="R26">
+        <f>Table1[[#This Row],[Promotion End Date]]-Table1[[#This Row],[Promotion Start Date]]</f>
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67DF188E-D298-4B5C-8FFD-6C2252898FD0}">
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr defaultRowHeight="15.75"/>
+  <cols>
+    <col min="1" max="1" width="19.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="18" width="10.125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="10.75" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2" s="5">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" s="5">
+        <v>48777.777777777781</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4" s="5">
+        <v>49625</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B5" s="5">
+        <v>49440</v>
       </c>
     </row>
   </sheetData>
